--- a/out/MLP-mamba2_repeat_3_000005.xlsx
+++ b/out/MLP-mamba2_repeat_3_000005.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.703898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.303898596494605</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.303898596494605</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6780933625747476</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37507,14 +37507,14 @@
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41489,7 +41489,7 @@
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6780933625747476</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43874,7 +43874,7 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45464,7 +45464,7 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47054,7 +47054,7 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54202,14 +54202,14 @@
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58979,7 +58979,7 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60569,7 +60569,7 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62152,14 +62152,14 @@
       </c>
       <c r="IZ77" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62947,14 +62947,14 @@
       </c>
       <c r="IZ78" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63749,7 +63749,7 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64544,7 +64544,7 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65339,7 +65339,7 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.703898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66929,7 +66929,7 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67724,7 +67724,7 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68519,7 +68519,7 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69314,7 +69314,7 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72494,7 +72494,7 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74077,14 +74077,14 @@
       </c>
       <c r="IZ92" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75674,7 +75674,7 @@
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.703898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78059,7 +78059,7 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79642,14 +79642,14 @@
       </c>
       <c r="IZ99" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82034,7 +82034,7 @@
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.303898596494605</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82829,7 +82829,7 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6780933625747476</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86797,14 +86797,14 @@
       </c>
       <c r="IZ108" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88387,14 +88387,14 @@
       </c>
       <c r="IZ110" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.303898596494605</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92369,7 +92369,7 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93959,7 +93959,7 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95542,14 +95542,14 @@
       </c>
       <c r="IZ119" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.303898596494605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96337,14 +96337,14 @@
       </c>
       <c r="IZ120" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.303898596494605</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.303898596494605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101107,14 +101107,14 @@
       </c>
       <c r="IZ126" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.278093362574747</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_3_000005.xlsx
+++ b/out/MLP-mamba2_repeat_3_000005.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683214</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>1</v>
       </c>
       <c r="JB8" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.5106925914798269</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="JB14" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683214</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>0</v>
       </c>
       <c r="JB20" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>1</v>
       </c>
       <c r="JB21" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18427,14 +18427,14 @@
       </c>
       <c r="IZ22" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA22" t="n">
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683221</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.02909442940683225</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683225</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683221</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.02909442940683221</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.02909442940683221</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931678</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>1</v>
       </c>
       <c r="JB32" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683207</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA38" t="n">
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683211</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31942,14 +31942,14 @@
       </c>
       <c r="IZ39" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA39" t="n">
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>0</v>
       </c>
       <c r="JB42" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>0</v>
       </c>
       <c r="JB43" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,7 +35924,7 @@
         <v>0</v>
       </c>
       <c r="JB44" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36719,7 +36719,7 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38309,7 +38309,7 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39104,7 +39104,7 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39899,7 +39899,7 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40694,7 +40694,7 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41482,14 +41482,14 @@
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA51" t="n">
         <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42284,7 +42284,7 @@
         <v>1</v>
       </c>
       <c r="JB52" t="n">
-        <v>2.303898596494605</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43072,14 +43072,14 @@
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA53" t="n">
         <v>0</v>
       </c>
       <c r="JB53" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.1709055705931679</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43867,14 +43867,14 @@
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA54" t="n">
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44669,7 +44669,7 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.303898596494605</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45457,14 +45457,14 @@
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA56" t="n">
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46259,7 +46259,7 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>2.303898596494605</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47047,14 +47047,14 @@
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA58" t="n">
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47849,7 +47849,7 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.303898596494605</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA60" t="n">
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49439,7 +49439,7 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50234,7 +50234,7 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51029,7 +51029,7 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51824,7 +51824,7 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52619,7 +52619,7 @@
         <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53414,7 +53414,7 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54209,7 +54209,7 @@
         <v>0</v>
       </c>
       <c r="JB67" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55004,7 +55004,7 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55799,7 +55799,7 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56594,7 +56594,7 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57389,7 +57389,7 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58184,7 +58184,7 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA73" t="n">
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59774,7 +59774,7 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.303898596494605</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60562,14 +60562,14 @@
       </c>
       <c r="IZ75" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA75" t="n">
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61364,7 +61364,7 @@
         <v>1</v>
       </c>
       <c r="JB76" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62159,7 +62159,7 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62954,7 +62954,7 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63742,14 +63742,14 @@
       </c>
       <c r="IZ79" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA79" t="n">
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64537,14 +64537,14 @@
       </c>
       <c r="IZ80" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA80" t="n">
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA81" t="n">
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66127,14 +66127,14 @@
       </c>
       <c r="IZ82" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA82" t="n">
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.6525037326661628</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA83" t="n">
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683203</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67717,14 +67717,14 @@
       </c>
       <c r="IZ84" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA84" t="n">
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.6525037326661628</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA85" t="n">
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683203</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69307,14 +69307,14 @@
       </c>
       <c r="IZ86" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA86" t="n">
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70109,7 +70109,7 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70904,7 +70904,7 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71699,7 +71699,7 @@
         <v>1</v>
       </c>
       <c r="JB89" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72487,14 +72487,14 @@
       </c>
       <c r="IZ90" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA90" t="n">
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73289,7 +73289,7 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74084,7 +74084,7 @@
         <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74879,7 +74879,7 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA94" t="n">
         <v>1</v>
       </c>
       <c r="JB94" t="n">
-        <v>1.703898596494605</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA95" t="n">
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.6525037326661628</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77264,7 +77264,7 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>2.303898596494605</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA97" t="n">
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.278093362574747</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78854,7 +78854,7 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79649,7 +79649,7 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80444,7 +80444,7 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81239,7 +81239,7 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683207</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82027,14 +82027,14 @@
       </c>
       <c r="IZ102" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA102" t="n">
         <v>1</v>
       </c>
       <c r="JB102" t="n">
-        <v>2.303898596494605</v>
+        <v>-0.02909442940683211</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82822,14 +82822,14 @@
       </c>
       <c r="IZ103" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA103" t="n">
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83624,7 +83624,7 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661628</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84419,7 +84419,7 @@
         <v>1</v>
       </c>
       <c r="JB105" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85207,14 +85207,14 @@
       </c>
       <c r="IZ106" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA106" t="n">
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86009,7 +86009,7 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6780933625747476</v>
+        <v>-0.5106925914798269</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86804,7 +86804,7 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87599,7 +87599,7 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88394,7 +88394,7 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89189,7 +89189,7 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89984,7 +89984,7 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90779,7 +90779,7 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.02909442940683207</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91574,7 +91574,7 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.303898596494605</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92362,14 +92362,14 @@
       </c>
       <c r="IZ115" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA115" t="n">
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93164,7 +93164,7 @@
         <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>2.303898596494605</v>
+        <v>0.170905570593168</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93952,14 +93952,14 @@
       </c>
       <c r="IZ117" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA117" t="n">
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.6780933625747476</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94754,7 +94754,7 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95549,7 +95549,7 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96344,7 +96344,7 @@
         <v>1</v>
       </c>
       <c r="JB120" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97139,7 +97139,7 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97934,7 +97934,7 @@
         <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98729,7 +98729,7 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.303898596494605</v>
+        <v>1.534101894739158</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99524,7 +99524,7 @@
         <v>1</v>
       </c>
       <c r="JB124" t="n">
-        <v>2.303898596494605</v>
+        <v>0.8525037326661629</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100319,7 +100319,7 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.029094429406832</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101114,7 +101114,7 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.278093362574747</v>
+        <v>-0.710692591479827</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_3_000005.xlsx
+++ b/out/MLP-mamba2_repeat_3_000005.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.432088702917099</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.4400000000000002</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4549160897731781</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.02909442940683214</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>1</v>
+        <v>0.6829301118850708</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.8525037326661628</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5006015300750732</v>
       </c>
       <c r="JB5" t="n">
-        <v>0.8525037326661628</v>
+        <v>-0.16</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.368901789188385</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5107680559158325</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>1</v>
+        <v>0.6853922605514526</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.2295231819152832</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.1709055705931679</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.3358798325061798</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.5106925914798269</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.2299230992794037</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.4348256587982178</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.2493017166852951</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0</v>
+        <v>0.3144731819629669</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.251363068819046</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.2567037045955658</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.02909442940683214</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.6751102805137634</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>1</v>
+        <v>0.5819530487060547</v>
       </c>
       <c r="JB18" t="n">
-        <v>1.534101894739158</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16046,10 +16046,10 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>1</v>
+        <v>0.8370569348335266</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0</v>
+        <v>0.4452733397483826</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>1</v>
+        <v>0.8073272705078125</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1709055705931679</v>
+        <v>0.3</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3357192277908325</v>
       </c>
       <c r="JB22" t="n">
-        <v>0.1709055705931679</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.2425922155380249</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.2971062958240509</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.02909442940683221</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5912857055664062</v>
       </c>
       <c r="JB25" t="n">
-        <v>-0.02909442940683225</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.4172161221504211</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.02909442940683225</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.2825391888618469</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.02909442940683221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>1</v>
+        <v>0.5576015114784241</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.02909442940683221</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23996,10 +23996,10 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3270767331123352</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.02909442940683221</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24791,10 +24791,10 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3741212785243988</v>
       </c>
       <c r="JB30" t="n">
-        <v>0.1709055705931678</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25586,10 +25586,10 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>1</v>
+        <v>0.5198750495910645</v>
       </c>
       <c r="JB31" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>1</v>
+        <v>0.8940069675445557</v>
       </c>
       <c r="JB32" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3673629462718964</v>
       </c>
       <c r="JB33" t="n">
-        <v>0.1709055705931679</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.1951543241739273</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.16</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28766,10 +28766,10 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.48568394780159</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29561,10 +29561,10 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.3304393291473389</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.1481636464595795</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.02909442940683207</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5572617650032043</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.02909442940683211</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.4582381844520569</v>
       </c>
       <c r="JB39" t="n">
-        <v>0.1709055705931679</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.2507252395153046</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.486711323261261</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.710692591479827</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0</v>
+        <v>0.3749862909317017</v>
       </c>
       <c r="JB42" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0</v>
+        <v>0.3565679490566254</v>
       </c>
       <c r="JB43" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,10 +35921,10 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0</v>
+        <v>0.2999575436115265</v>
       </c>
       <c r="JB44" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC44" t="n">
         <v>0</v>
@@ -36716,10 +36716,10 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.2766838073730469</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC45" t="n">
         <v>0</v>
@@ -37511,10 +37511,10 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.4298914968967438</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC46" t="n">
         <v>0</v>
@@ -38306,10 +38306,10 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.3078060448169708</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC47" t="n">
         <v>0</v>
@@ -39101,10 +39101,10 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.3749707937240601</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC48" t="n">
         <v>0</v>
@@ -39896,10 +39896,10 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.2872630655765533</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC49" t="n">
         <v>0</v>
@@ -40691,10 +40691,10 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.2695160210132599</v>
       </c>
       <c r="JB50" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC50" t="n">
         <v>0</v>
@@ -41486,10 +41486,10 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0</v>
+        <v>0.3319984078407288</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.170905570593168</v>
+        <v>0.16</v>
       </c>
       <c r="JC51" t="n">
         <v>0</v>
@@ -42281,10 +42281,10 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>1</v>
+        <v>0.5037586688995361</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.1709055705931679</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC52" t="n">
         <v>0</v>
@@ -43076,10 +43076,10 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0</v>
+        <v>0.4011089503765106</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.1709055705931679</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC53" t="n">
         <v>0</v>
@@ -43871,10 +43871,10 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.2790795862674713</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.170905570593168</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
         <v>0</v>
@@ -44666,10 +44666,10 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.5146570801734924</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.170905570593168</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC55" t="n">
         <v>0</v>
@@ -45461,10 +45461,10 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.2530079185962677</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.16</v>
       </c>
       <c r="JC56" t="n">
         <v>0</v>
@@ -46256,10 +46256,10 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.6751461029052734</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.170905570593168</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC57" t="n">
         <v>0</v>
@@ -47051,10 +47051,10 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.2930324971675873</v>
       </c>
       <c r="JB58" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.3</v>
       </c>
       <c r="JC58" t="n">
         <v>0</v>
@@ -47846,10 +47846,10 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.5227110385894775</v>
       </c>
       <c r="JB59" t="n">
-        <v>0.170905570593168</v>
+        <v>0.3</v>
       </c>
       <c r="JC59" t="n">
         <v>0</v>
@@ -48637,14 +48637,14 @@
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.4916534125804901</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.170905570593168</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC60" t="n">
         <v>0</v>
@@ -49436,10 +49436,10 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.2716105878353119</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC61" t="n">
         <v>0</v>
@@ -50231,10 +50231,10 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.2688597440719604</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC62" t="n">
         <v>0</v>
@@ -51026,10 +51026,10 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.3076213002204895</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC63" t="n">
         <v>0</v>
@@ -51821,10 +51821,10 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3186903297901154</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC64" t="n">
         <v>0</v>
@@ -52616,10 +52616,10 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0</v>
+        <v>0.3015494346618652</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC65" t="n">
         <v>0</v>
@@ -53411,10 +53411,10 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.2930974364280701</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC66" t="n">
         <v>0</v>
@@ -54206,10 +54206,10 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0</v>
+        <v>0.4015712440013885</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC67" t="n">
         <v>0</v>
@@ -55001,10 +55001,10 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.2938527762889862</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
         <v>0</v>
@@ -55792,14 +55792,14 @@
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.269543468952179</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC69" t="n">
         <v>0</v>
@@ -56591,10 +56591,10 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3362481892108917</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC70" t="n">
         <v>0</v>
@@ -57386,10 +57386,10 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.2330296337604523</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC71" t="n">
         <v>0</v>
@@ -58181,10 +58181,10 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.1415454745292664</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
         <v>0</v>
@@ -58972,14 +58972,14 @@
       </c>
       <c r="IZ73" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.1621725410223007</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.170905570593168</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC73" t="n">
         <v>0</v>
@@ -59771,10 +59771,10 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.7769520878791809</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.170905570593168</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC74" t="n">
         <v>0</v>
@@ -60566,10 +60566,10 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.3359872400760651</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC75" t="n">
         <v>0</v>
@@ -61361,10 +61361,10 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>1</v>
+        <v>0.8113314509391785</v>
       </c>
       <c r="JB76" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
         <v>0</v>
@@ -62156,10 +62156,10 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.589716374874115</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.534101894739158</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC77" t="n">
         <v>0</v>
@@ -62951,10 +62951,10 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.6033487915992737</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC78" t="n">
         <v>0</v>
@@ -63746,10 +63746,10 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.423809289932251</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.170905570593168</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC79" t="n">
         <v>0</v>
@@ -64541,10 +64541,10 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4366397559642792</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.170905570593168</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC80" t="n">
         <v>0</v>
@@ -65332,14 +65332,14 @@
       </c>
       <c r="IZ81" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5040635466575623</v>
       </c>
       <c r="JB81" t="n">
-        <v>-0.029094429406832</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
         <v>0</v>
@@ -66131,10 +66131,10 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.3547540605068207</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.6525037326661628</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC82" t="n">
         <v>0</v>
@@ -66922,14 +66922,14 @@
       </c>
       <c r="IZ83" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.6952264308929443</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.02909442940683203</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC83" t="n">
         <v>0</v>
@@ -67721,10 +67721,10 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.4930078387260437</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.6525037326661628</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC84" t="n">
         <v>0</v>
@@ -68512,14 +68512,14 @@
       </c>
       <c r="IZ85" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.7009465098381042</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.02909442940683203</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC85" t="n">
         <v>0</v>
@@ -69311,10 +69311,10 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4344556629657745</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC86" t="n">
         <v>0</v>
@@ -70106,10 +70106,10 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.6331809163093567</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC87" t="n">
         <v>0</v>
@@ -70901,10 +70901,10 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7642132043838501</v>
       </c>
       <c r="JB88" t="n">
-        <v>1.534101894739158</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
         <v>0</v>
@@ -71696,10 +71696,10 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>1</v>
+        <v>0.6450920701026917</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC89" t="n">
         <v>0</v>
@@ -72491,10 +72491,10 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.2858415246009827</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.170905570593168</v>
+        <v>-0.3</v>
       </c>
       <c r="JC90" t="n">
         <v>0</v>
@@ -73286,10 +73286,10 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.3216298520565033</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC91" t="n">
         <v>0</v>
@@ -74081,10 +74081,10 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0</v>
+        <v>0.4683062136173248</v>
       </c>
       <c r="JB92" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC92" t="n">
         <v>0</v>
@@ -74876,10 +74876,10 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3630078136920929</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC93" t="n">
         <v>0</v>
@@ -75667,14 +75667,14 @@
       </c>
       <c r="IZ94" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>1</v>
+        <v>0.5891309976577759</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.16</v>
       </c>
       <c r="JC94" t="n">
         <v>0</v>
@@ -76462,14 +76462,14 @@
       </c>
       <c r="IZ95" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.4941951036453247</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.6525037326661628</v>
+        <v>-0.3</v>
       </c>
       <c r="JC95" t="n">
         <v>0</v>
@@ -77261,10 +77261,10 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.7352268695831299</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.170905570593168</v>
+        <v>0.3</v>
       </c>
       <c r="JC96" t="n">
         <v>0</v>
@@ -78052,14 +78052,14 @@
       </c>
       <c r="IZ97" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.3722044229507446</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.170905570593168</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
         <v>0</v>
@@ -78851,10 +78851,10 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.409857839345932</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
         <v>0</v>
@@ -79646,10 +79646,10 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.4755758345127106</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC99" t="n">
         <v>0</v>
@@ -80441,10 +80441,10 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4478019773960114</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC100" t="n">
         <v>0</v>
@@ -81236,10 +81236,10 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.3092822730541229</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.02909442940683207</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
         <v>0</v>
@@ -82031,10 +82031,10 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>1</v>
+        <v>0.7523510456085205</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.02909442940683211</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC102" t="n">
         <v>0</v>
@@ -82826,10 +82826,10 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.4275355041027069</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC103" t="n">
         <v>0</v>
@@ -83621,10 +83621,10 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.5236124992370605</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.8525037326661628</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC104" t="n">
         <v>0</v>
@@ -84416,10 +84416,10 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>1</v>
+        <v>0.6218529343605042</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC105" t="n">
         <v>0</v>
@@ -85211,10 +85211,10 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4512673914432526</v>
       </c>
       <c r="JB106" t="n">
-        <v>0.170905570593168</v>
+        <v>0.16</v>
       </c>
       <c r="JC106" t="n">
         <v>0</v>
@@ -86002,14 +86002,14 @@
       </c>
       <c r="IZ107" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.4581573903560638</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.5106925914798269</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC107" t="n">
         <v>0</v>
@@ -86801,10 +86801,10 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3987685143947601</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC108" t="n">
         <v>0</v>
@@ -87596,10 +87596,10 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.3744718432426453</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC109" t="n">
         <v>0</v>
@@ -88391,10 +88391,10 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4268379211425781</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC110" t="n">
         <v>0</v>
@@ -89186,10 +89186,10 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3215245306491852</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC111" t="n">
         <v>0</v>
@@ -89981,10 +89981,10 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.3387529850006104</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.710692591479827</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC112" t="n">
         <v>0</v>
@@ -90776,10 +90776,10 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3385855257511139</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.02909442940683207</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC113" t="n">
         <v>0</v>
@@ -91571,10 +91571,10 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.8408265113830566</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.170905570593168</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
         <v>0</v>
@@ -92366,10 +92366,10 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3747356832027435</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
         <v>0</v>
@@ -93161,10 +93161,10 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>1</v>
+        <v>0.9402955770492554</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.170905570593168</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
         <v>0</v>
@@ -93956,10 +93956,10 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.4305267035961151</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.3</v>
       </c>
       <c r="JC117" t="n">
         <v>0</v>
@@ -94751,10 +94751,10 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.7941454648971558</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC118" t="n">
         <v>0</v>
@@ -95546,10 +95546,10 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.5028966069221497</v>
       </c>
       <c r="JB119" t="n">
-        <v>1.534101894739158</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC119" t="n">
         <v>0</v>
@@ -96341,10 +96341,10 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>1</v>
+        <v>0.5883155465126038</v>
       </c>
       <c r="JB120" t="n">
-        <v>1.534101894739158</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
         <v>0</v>
@@ -97136,10 +97136,10 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.5446981191635132</v>
       </c>
       <c r="JB121" t="n">
-        <v>1.534101894739158</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC121" t="n">
         <v>0</v>
@@ -97931,10 +97931,10 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>1</v>
+        <v>0.9028095006942749</v>
       </c>
       <c r="JB122" t="n">
-        <v>1.534101894739158</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC122" t="n">
         <v>0</v>
@@ -98726,10 +98726,10 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.727616012096405</v>
       </c>
       <c r="JB123" t="n">
-        <v>1.534101894739158</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
         <v>0</v>
@@ -99521,10 +99521,10 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>1</v>
+        <v>0.9069597721099854</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.8525037326661629</v>
+        <v>0.3</v>
       </c>
       <c r="JC124" t="n">
         <v>0</v>
@@ -100316,10 +100316,10 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3053939640522003</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.029094429406832</v>
+        <v>-0.6500000000000004</v>
       </c>
       <c r="JC125" t="n">
         <v>0</v>
@@ -101111,10 +101111,10 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4550611972808838</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.710692591479827</v>
+        <v>-1</v>
       </c>
       <c r="JC126" t="n">
         <v>0</v>

--- a/out/MLP-mamba2_repeat_3_000005.xlsx
+++ b/out/MLP-mamba2_repeat_3_000005.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.432088702917099</v>
+        <v>0.4320887923240662</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4400000000000002</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4549160897731781</v>
+        <v>0.4549164175987244</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.4400000000000001</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.5006015300750732</v>
+        <v>0.5006018280982971</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.16</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.368901789188385</v>
+        <v>0.3689017295837402</v>
       </c>
       <c r="JB6" t="n">
         <v>0.5799999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.5107680559158325</v>
+        <v>0.5107681155204773</v>
       </c>
       <c r="JB7" t="n">
         <v>0.3</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.6853922605514526</v>
+        <v>0.685392439365387</v>
       </c>
       <c r="JB8" t="n">
         <v>0.1600000000000001</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.2295231819152832</v>
+        <v>0.229523241519928</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.4399999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.2299230992794037</v>
+        <v>0.2299230396747589</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.9999999999999998</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.4348256587982178</v>
+        <v>0.4348255693912506</v>
       </c>
       <c r="JB12" t="n">
         <v>-0.9999999999999998</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.2493017166852951</v>
+        <v>0.2493015974760056</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.9999999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.3144731819629669</v>
+        <v>0.3144730627536774</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.9999999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.251363068819046</v>
+        <v>0.2513629496097565</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.2567037045955658</v>
+        <v>0.2567035257816315</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.6751102805137634</v>
+        <v>0.6751105189323425</v>
       </c>
       <c r="JB17" t="n">
         <v>0.4399999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.5819530487060547</v>
+        <v>0.5819531679153442</v>
       </c>
       <c r="JB18" t="n">
         <v>0.5799999999999998</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.8370569348335266</v>
+        <v>0.8370563387870789</v>
       </c>
       <c r="JB19" t="n">
         <v>0.8599999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.4452733397483826</v>
+        <v>0.4452740252017975</v>
       </c>
       <c r="JB20" t="n">
         <v>0.5799999999999998</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.8073272705078125</v>
+        <v>0.8073262572288513</v>
       </c>
       <c r="JB21" t="n">
         <v>0.3</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.3357192277908325</v>
+        <v>0.33571857213974</v>
       </c>
       <c r="JB22" t="n">
         <v>0.02000000000000007</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.2425922155380249</v>
+        <v>0.2425923943519592</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.4399999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.2971062958240509</v>
+        <v>0.297106146812439</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.7199999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.5912857055664062</v>
+        <v>0.5912858247756958</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.4172161221504211</v>
+        <v>0.4172159731388092</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.4399999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.5576015114784241</v>
+        <v>0.5576016902923584</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.3270767331123352</v>
+        <v>0.327076643705368</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.4399999999999999</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.5198750495910645</v>
+        <v>0.519875168800354</v>
       </c>
       <c r="JB31" t="n">
         <v>0.1600000000000001</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.8940069675445557</v>
+        <v>0.8940061330795288</v>
       </c>
       <c r="JB32" t="n">
         <v>0.1600000000000001</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3673629462718964</v>
+        <v>0.3673644363880157</v>
       </c>
       <c r="JB33" t="n">
         <v>0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.1951543241739273</v>
+        <v>0.1951552927494049</v>
       </c>
       <c r="JB34" t="n">
         <v>0.16</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.48568394780159</v>
+        <v>0.4856841862201691</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.7199999999999999</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.3304393291473389</v>
+        <v>0.3304391801357269</v>
       </c>
       <c r="JB36" t="n">
         <v>-0.4399999999999999</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.1481636464595795</v>
+        <v>0.1481637507677078</v>
       </c>
       <c r="JB37" t="n">
         <v>-0.1600000000000001</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.5572617650032043</v>
+        <v>0.5572617053985596</v>
       </c>
       <c r="JB38" t="n">
         <v>0.1600000000000001</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.4582381844520569</v>
+        <v>0.4582381248474121</v>
       </c>
       <c r="JB39" t="n">
         <v>0.4399999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.2507252395153046</v>
+        <v>0.2507252991199493</v>
       </c>
       <c r="JB40" t="n">
         <v>0.4399999999999999</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.486711323261261</v>
+        <v>0.4867114424705505</v>
       </c>
       <c r="JB41" t="n">
         <v>0.1600000000000001</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.3749862909317017</v>
+        <v>0.3749863505363464</v>
       </c>
       <c r="JB42" t="n">
         <v>-0.7199999999999999</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.3565679490566254</v>
+        <v>0.356567919254303</v>
       </c>
       <c r="JB43" t="n">
         <v>-0.7199999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.2999575436115265</v>
+        <v>0.2999573349952698</v>
       </c>
       <c r="JB44" t="n">
         <v>-0.9999999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.2766838073730469</v>
+        <v>0.2766837179660797</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.9999999999999998</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.4298914968967438</v>
+        <v>0.4298913180828094</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.9999999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.3078060448169708</v>
+        <v>0.3078058660030365</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.9999999999999998</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.3749707937240601</v>
+        <v>0.3749704658985138</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.9999999999999998</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.2872630655765533</v>
+        <v>0.287262886762619</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.9999999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.2695160210132599</v>
+        <v>0.2695159018039703</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.7199999999999999</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.3319984078407288</v>
+        <v>0.3319982290267944</v>
       </c>
       <c r="JB51" t="n">
         <v>0.16</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.4011089503765106</v>
+        <v>0.4011088013648987</v>
       </c>
       <c r="JB53" t="n">
         <v>0.4399999999999999</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.2790795862674713</v>
+        <v>0.2790794372558594</v>
       </c>
       <c r="JB54" t="n">
         <v>0.4399999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.5146570801734924</v>
+        <v>0.5146571397781372</v>
       </c>
       <c r="JB55" t="n">
         <v>0.4399999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.2530079185962677</v>
+        <v>0.2530077397823334</v>
       </c>
       <c r="JB56" t="n">
         <v>0.16</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.6751461029052734</v>
+        <v>0.6751465201377869</v>
       </c>
       <c r="JB57" t="n">
         <v>0.4399999999999999</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.2930324971675873</v>
+        <v>0.2930325865745544</v>
       </c>
       <c r="JB58" t="n">
         <v>0.3</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.5227110385894775</v>
+        <v>0.5227112174034119</v>
       </c>
       <c r="JB59" t="n">
         <v>0.3</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.4916534125804901</v>
+        <v>0.4916535019874573</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.5799999999999998</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.2716105878353119</v>
+        <v>0.2716105580329895</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.5799999999999998</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.2688597440719604</v>
+        <v>0.2688598334789276</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.8599999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.3076213002204895</v>
+        <v>0.3076210618019104</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.9999999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3186903297901154</v>
+        <v>0.3186900913715363</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.9999999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.3015494346618652</v>
+        <v>0.3015488684177399</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.7199999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.2930974364280701</v>
+        <v>0.2930971086025238</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.7199999999999999</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.4015712440013885</v>
+        <v>0.4015710353851318</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.7199999999999999</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.2938527762889862</v>
+        <v>0.2938525378704071</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.269543468952179</v>
+        <v>0.2695432007312775</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.1199999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.3362481892108917</v>
+        <v>0.3362481296062469</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.9999999999999998</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.2330296337604523</v>
+        <v>0.2330294698476791</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.9999999999999998</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.1415454745292664</v>
+        <v>0.1415452063083649</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.1621725410223007</v>
+        <v>0.1621723771095276</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.7199999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.7769520878791809</v>
+        <v>0.776952862739563</v>
       </c>
       <c r="JB74" t="n">
         <v>0.1600000000000001</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.3359872400760651</v>
+        <v>0.3359881341457367</v>
       </c>
       <c r="JB75" t="n">
         <v>0.4399999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.8113314509391785</v>
+        <v>0.8113320469856262</v>
       </c>
       <c r="JB76" t="n">
         <v>0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.589716374874115</v>
+        <v>0.5897178053855896</v>
       </c>
       <c r="JB77" t="n">
         <v>0.5799999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.6033487915992737</v>
+        <v>0.6033498644828796</v>
       </c>
       <c r="JB78" t="n">
         <v>0.8599999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.423809289932251</v>
+        <v>0.4238101840019226</v>
       </c>
       <c r="JB79" t="n">
         <v>0.7199999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.4366397559642792</v>
+        <v>0.4366404116153717</v>
       </c>
       <c r="JB80" t="n">
         <v>0.4399999999999999</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.5040635466575623</v>
+        <v>0.5040642619132996</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.3547540605068207</v>
+        <v>0.3547547161579132</v>
       </c>
       <c r="JB82" t="n">
         <v>0.5799999999999998</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.6952264308929443</v>
+        <v>0.6952271461486816</v>
       </c>
       <c r="JB83" t="n">
         <v>-0.02000000000000007</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.4930078387260437</v>
+        <v>0.4930085837841034</v>
       </c>
       <c r="JB84" t="n">
         <v>-0.02000000000000007</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.7009465098381042</v>
+        <v>0.7009470462799072</v>
       </c>
       <c r="JB85" t="n">
         <v>0.8599999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.4344556629657745</v>
+        <v>0.4344563186168671</v>
       </c>
       <c r="JB86" t="n">
         <v>0.8599999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.6331809163093567</v>
+        <v>0.6331811547279358</v>
       </c>
       <c r="JB87" t="n">
         <v>0.8599999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.7642132043838501</v>
+        <v>0.7642139792442322</v>
       </c>
       <c r="JB88" t="n">
         <v>0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.6450920701026917</v>
+        <v>0.6450929045677185</v>
       </c>
       <c r="JB89" t="n">
         <v>0.4399999999999999</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.2858415246009827</v>
+        <v>0.2858421802520752</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.3</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.3216298520565033</v>
+        <v>0.3216303586959839</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.5799999999999998</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.4683062136173248</v>
+        <v>0.468306839466095</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.7199999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3630078136920929</v>
+        <v>0.3630083799362183</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.4399999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.5891309976577759</v>
+        <v>0.5891314744949341</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.4941951036453247</v>
+        <v>0.4941957294940948</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.3</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.7352268695831299</v>
+        <v>0.7352274060249329</v>
       </c>
       <c r="JB96" t="n">
         <v>0.3</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.3722044229507446</v>
+        <v>0.3722050487995148</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.409857839345932</v>
+        <v>0.4098584055900574</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.4755758345127106</v>
+        <v>0.4755765795707703</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.9999999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4478019773960114</v>
+        <v>0.4478024542331696</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.7199999999999999</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.3092822730541229</v>
+        <v>0.3092828094959259</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.7523510456085205</v>
+        <v>0.7523515224456787</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.4399999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.4275355041027069</v>
+        <v>0.4275361299514771</v>
       </c>
       <c r="JB103" t="n">
         <v>0.4399999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.5236124992370605</v>
+        <v>0.5236131548881531</v>
       </c>
       <c r="JB104" t="n">
         <v>0.4399999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.6218529343605042</v>
+        <v>0.6218535304069519</v>
       </c>
       <c r="JB105" t="n">
         <v>0.1600000000000001</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4512673914432526</v>
+        <v>0.4512682855129242</v>
       </c>
       <c r="JB106" t="n">
         <v>0.16</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.4581573903560638</v>
+        <v>0.4581580460071564</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.1199999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3987685143947601</v>
+        <v>0.3987693190574646</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.9999999999999998</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.3744718432426453</v>
+        <v>0.3744725584983826</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.9999999999999998</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.4268379211425781</v>
+        <v>0.426838606595993</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.9999999999999998</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.3215245306491852</v>
+        <v>0.3215250074863434</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.9999999999999998</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.3387529850006104</v>
+        <v>0.3387534916400909</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.7199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.3385855257511139</v>
+        <v>0.3385860919952393</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.7199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.8408265113830566</v>
+        <v>0.8408268094062805</v>
       </c>
       <c r="JB114" t="n">
         <v>0.1600000000000001</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.3747356832027435</v>
+        <v>0.3747369945049286</v>
       </c>
       <c r="JB115" t="n">
         <v>0.16</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.4305267035961151</v>
+        <v>0.4305284917354584</v>
       </c>
       <c r="JB117" t="n">
         <v>0.3</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.7941454648971558</v>
+        <v>0.7941457629203796</v>
       </c>
       <c r="JB118" t="n">
         <v>0.5799999999999998</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.5028966069221497</v>
+        <v>0.5028983950614929</v>
       </c>
       <c r="JB119" t="n">
         <v>0.4399999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.5883155465126038</v>
+        <v>0.5883161425590515</v>
       </c>
       <c r="JB120" t="n">
         <v>0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.5446981191635132</v>
+        <v>0.5446984767913818</v>
       </c>
       <c r="JB121" t="n">
         <v>0.5799999999999998</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.9028095006942749</v>
+        <v>0.9028097987174988</v>
       </c>
       <c r="JB122" t="n">
         <v>0.7199999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.727616012096405</v>
+        <v>0.7276170253753662</v>
       </c>
       <c r="JB123" t="n">
         <v>0.4399999999999999</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.3053939640522003</v>
+        <v>0.3053954541683197</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.6500000000000004</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4550611972808838</v>
+        <v>0.4550617337226868</v>
       </c>
       <c r="JB126" t="n">
         <v>-1</v>
